--- a/artfynd/A 55345-2020 artfynd.xlsx
+++ b/artfynd/A 55345-2020 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 55345-2020 artfynd.xlsx
+++ b/artfynd/A 55345-2020 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY579"/>
+  <dimension ref="A1:AY582"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -63731,6 +63731,327 @@
       </c>
       <c r="AY579" t="inlineStr"/>
     </row>
+    <row r="580">
+      <c r="A580" t="n">
+        <v>128759661</v>
+      </c>
+      <c r="B580" t="n">
+        <v>90093</v>
+      </c>
+      <c r="D580" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E580" t="n">
+        <v>4962</v>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>Mjölsvärting</t>
+        </is>
+      </c>
+      <c r="G580" t="inlineStr">
+        <is>
+          <t>Lyophyllum semitale</t>
+        </is>
+      </c>
+      <c r="H580" t="inlineStr">
+        <is>
+          <t>(Fr. : Fr.) Kühner</t>
+        </is>
+      </c>
+      <c r="I580" t="inlineStr"/>
+      <c r="P580" t="inlineStr">
+        <is>
+          <t>Sikån, Sikån, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q580" t="n">
+        <v>725323</v>
+      </c>
+      <c r="R580" t="n">
+        <v>7332652</v>
+      </c>
+      <c r="S580" t="n">
+        <v>10</v>
+      </c>
+      <c r="T580" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U580" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V580" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W580" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y580" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z580" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AA580" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB580" t="inlineStr">
+        <is>
+          <t>15:44</t>
+        </is>
+      </c>
+      <c r="AD580" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE580" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG580" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT580" t="inlineStr"/>
+      <c r="AW580" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX580" t="inlineStr">
+        <is>
+          <t>Sara Forsström, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY580" t="inlineStr"/>
+    </row>
+    <row r="581">
+      <c r="A581" t="n">
+        <v>128758618</v>
+      </c>
+      <c r="B581" t="n">
+        <v>90278</v>
+      </c>
+      <c r="D581" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E581" t="n">
+        <v>245044</v>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>Tallmusseron</t>
+        </is>
+      </c>
+      <c r="G581" t="inlineStr">
+        <is>
+          <t>Tricholoma roseoacerbum</t>
+        </is>
+      </c>
+      <c r="H581" t="inlineStr">
+        <is>
+          <t>A.Riva</t>
+        </is>
+      </c>
+      <c r="I581" t="inlineStr"/>
+      <c r="P581" t="inlineStr">
+        <is>
+          <t>Norden, Norden, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q581" t="n">
+        <v>725377</v>
+      </c>
+      <c r="R581" t="n">
+        <v>7332589</v>
+      </c>
+      <c r="S581" t="n">
+        <v>10</v>
+      </c>
+      <c r="T581" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U581" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V581" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W581" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y581" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z581" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AA581" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB581" t="inlineStr">
+        <is>
+          <t>15:07</t>
+        </is>
+      </c>
+      <c r="AD581" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE581" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG581" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT581" t="inlineStr"/>
+      <c r="AW581" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX581" t="inlineStr">
+        <is>
+          <t>Sara Forsström, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY581" t="inlineStr"/>
+    </row>
+    <row r="582">
+      <c r="A582" t="n">
+        <v>128759259</v>
+      </c>
+      <c r="B582" t="n">
+        <v>88773</v>
+      </c>
+      <c r="D582" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E582" t="n">
+        <v>816</v>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>Smultronkantarell</t>
+        </is>
+      </c>
+      <c r="G582" t="inlineStr">
+        <is>
+          <t>Aphroditeola olida</t>
+        </is>
+      </c>
+      <c r="H582" t="inlineStr">
+        <is>
+          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
+        </is>
+      </c>
+      <c r="I582" t="inlineStr"/>
+      <c r="P582" t="inlineStr">
+        <is>
+          <t>Norden, Norden, Lu lm</t>
+        </is>
+      </c>
+      <c r="Q582" t="n">
+        <v>725293</v>
+      </c>
+      <c r="R582" t="n">
+        <v>7332591</v>
+      </c>
+      <c r="S582" t="n">
+        <v>10</v>
+      </c>
+      <c r="T582" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U582" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="V582" t="inlineStr">
+        <is>
+          <t>Lule lappmark</t>
+        </is>
+      </c>
+      <c r="W582" t="inlineStr">
+        <is>
+          <t>Jokkmokk</t>
+        </is>
+      </c>
+      <c r="Y582" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="Z582" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AA582" t="inlineStr">
+        <is>
+          <t>2025-09-28</t>
+        </is>
+      </c>
+      <c r="AB582" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AD582" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE582" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG582" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT582" t="inlineStr"/>
+      <c r="AW582" t="inlineStr">
+        <is>
+          <t>Sara Forsström</t>
+        </is>
+      </c>
+      <c r="AX582" t="inlineStr">
+        <is>
+          <t>Sara Forsström, Isak Vahlström</t>
+        </is>
+      </c>
+      <c r="AY582" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 55345-2020 artfynd.xlsx
+++ b/artfynd/A 55345-2020 artfynd.xlsx
@@ -63736,7 +63736,7 @@
         <v>128759661</v>
       </c>
       <c r="B580" t="n">
-        <v>90093</v>
+        <v>90120</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -63833,7 +63833,7 @@
       </c>
       <c r="AX580" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY580" t="inlineStr"/>
@@ -63843,7 +63843,7 @@
         <v>128758618</v>
       </c>
       <c r="B581" t="n">
-        <v>90278</v>
+        <v>90305</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -63950,7 +63950,7 @@
         <v>128759259</v>
       </c>
       <c r="B582" t="n">
-        <v>88773</v>
+        <v>88800</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>

--- a/artfynd/A 55345-2020 artfynd.xlsx
+++ b/artfynd/A 55345-2020 artfynd.xlsx
@@ -63833,7 +63833,7 @@
       </c>
       <c r="AX580" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Sara Forsström, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY580" t="inlineStr"/>

--- a/artfynd/A 55345-2020 artfynd.xlsx
+++ b/artfynd/A 55345-2020 artfynd.xlsx
@@ -63736,7 +63736,7 @@
         <v>128759661</v>
       </c>
       <c r="B580" t="n">
-        <v>90120</v>
+        <v>90125</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -63843,7 +63843,7 @@
         <v>128758618</v>
       </c>
       <c r="B581" t="n">
-        <v>90305</v>
+        <v>90310</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -63950,7 +63950,7 @@
         <v>128759259</v>
       </c>
       <c r="B582" t="n">
-        <v>88800</v>
+        <v>88804</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>

--- a/artfynd/A 55345-2020 artfynd.xlsx
+++ b/artfynd/A 55345-2020 artfynd.xlsx
@@ -63736,7 +63736,7 @@
         <v>128759661</v>
       </c>
       <c r="B580" t="n">
-        <v>90125</v>
+        <v>90130</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -63843,7 +63843,7 @@
         <v>128758618</v>
       </c>
       <c r="B581" t="n">
-        <v>90310</v>
+        <v>90315</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -63950,7 +63950,7 @@
         <v>128759259</v>
       </c>
       <c r="B582" t="n">
-        <v>88804</v>
+        <v>88805</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>

--- a/artfynd/A 55345-2020 artfynd.xlsx
+++ b/artfynd/A 55345-2020 artfynd.xlsx
@@ -63736,7 +63736,7 @@
         <v>128759661</v>
       </c>
       <c r="B580" t="n">
-        <v>90130</v>
+        <v>90134</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -63843,7 +63843,7 @@
         <v>128758618</v>
       </c>
       <c r="B581" t="n">
-        <v>90315</v>
+        <v>90319</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -63950,7 +63950,7 @@
         <v>128759259</v>
       </c>
       <c r="B582" t="n">
-        <v>88805</v>
+        <v>88809</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>

--- a/artfynd/A 55345-2020 artfynd.xlsx
+++ b/artfynd/A 55345-2020 artfynd.xlsx
@@ -63736,7 +63736,7 @@
         <v>128759661</v>
       </c>
       <c r="B580" t="n">
-        <v>90134</v>
+        <v>90139</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -63843,7 +63843,7 @@
         <v>128758618</v>
       </c>
       <c r="B581" t="n">
-        <v>90319</v>
+        <v>90324</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -63950,7 +63950,7 @@
         <v>128759259</v>
       </c>
       <c r="B582" t="n">
-        <v>88809</v>
+        <v>88814</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>

--- a/artfynd/A 55345-2020 artfynd.xlsx
+++ b/artfynd/A 55345-2020 artfynd.xlsx
@@ -65133,45 +65133,54 @@
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>129083490</v>
+        <v>129083486</v>
       </c>
       <c r="B593" t="n">
-        <v>91681</v>
+        <v>57827</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E593" t="n">
-        <v>1503</v>
+        <v>103031</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I593" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M593" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P593" t="inlineStr">
         <is>
           <t>Piellojaure, Lu lm</t>
         </is>
       </c>
       <c r="Q593" t="n">
-        <v>725370</v>
+        <v>725293</v>
       </c>
       <c r="R593" t="n">
-        <v>7332593</v>
+        <v>7332592</v>
       </c>
       <c r="S593" t="n">
         <v>25</v>
@@ -65203,7 +65212,7 @@
       </c>
       <c r="Z593" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA593" t="inlineStr">
@@ -65213,7 +65222,7 @@
       </c>
       <c r="AB593" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD593" t="b">
@@ -65240,54 +65249,45 @@
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>129083486</v>
+        <v>129083490</v>
       </c>
       <c r="B594" t="n">
-        <v>57827</v>
+        <v>91681</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E594" t="n">
-        <v>103031</v>
+        <v>1503</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I594" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M594" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr"/>
       <c r="P594" t="inlineStr">
         <is>
           <t>Piellojaure, Lu lm</t>
         </is>
       </c>
       <c r="Q594" t="n">
-        <v>725293</v>
+        <v>725370</v>
       </c>
       <c r="R594" t="n">
-        <v>7332592</v>
+        <v>7332593</v>
       </c>
       <c r="S594" t="n">
         <v>25</v>
@@ -65319,7 +65319,7 @@
       </c>
       <c r="Z594" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA594" t="inlineStr">
@@ -65329,7 +65329,7 @@
       </c>
       <c r="AB594" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD594" t="b">

--- a/artfynd/A 55345-2020 artfynd.xlsx
+++ b/artfynd/A 55345-2020 artfynd.xlsx
@@ -63736,7 +63736,7 @@
         <v>128759661</v>
       </c>
       <c r="B580" t="n">
-        <v>90146</v>
+        <v>90149</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -63843,7 +63843,7 @@
         <v>128758618</v>
       </c>
       <c r="B581" t="n">
-        <v>90331</v>
+        <v>90334</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -63950,7 +63950,7 @@
         <v>128759259</v>
       </c>
       <c r="B582" t="n">
-        <v>88821</v>
+        <v>88824</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -64057,7 +64057,7 @@
         <v>129083488</v>
       </c>
       <c r="B583" t="n">
-        <v>90552</v>
+        <v>90555</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -64164,7 +64164,7 @@
         <v>129083492</v>
       </c>
       <c r="B584" t="n">
-        <v>91681</v>
+        <v>91684</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -64378,7 +64378,7 @@
         <v>129083483</v>
       </c>
       <c r="B586" t="n">
-        <v>90552</v>
+        <v>90555</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -64485,7 +64485,7 @@
         <v>129083493</v>
       </c>
       <c r="B587" t="n">
-        <v>90552</v>
+        <v>90555</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -64592,7 +64592,7 @@
         <v>129083482</v>
       </c>
       <c r="B588" t="n">
-        <v>92815</v>
+        <v>92820</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -64922,7 +64922,7 @@
         <v>129083477</v>
       </c>
       <c r="B591" t="n">
-        <v>90552</v>
+        <v>90555</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -65029,7 +65029,7 @@
         <v>129083485</v>
       </c>
       <c r="B592" t="n">
-        <v>90146</v>
+        <v>90149</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -65252,7 +65252,7 @@
         <v>129083490</v>
       </c>
       <c r="B594" t="n">
-        <v>91681</v>
+        <v>91684</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -65356,32 +65356,32 @@
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>129083489</v>
+        <v>129083484</v>
       </c>
       <c r="B595" t="n">
-        <v>92805</v>
+        <v>88824</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E595" t="n">
-        <v>4362</v>
+        <v>816</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smultronkantarell</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Aphroditeola olida</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
         </is>
       </c>
       <c r="I595" t="inlineStr"/>
@@ -65391,10 +65391,10 @@
         </is>
       </c>
       <c r="Q595" t="n">
-        <v>725414</v>
+        <v>725274</v>
       </c>
       <c r="R595" t="n">
-        <v>7332615</v>
+        <v>7332631</v>
       </c>
       <c r="S595" t="n">
         <v>25</v>
@@ -65426,7 +65426,7 @@
       </c>
       <c r="Z595" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA595" t="inlineStr">
@@ -65436,7 +65436,7 @@
       </c>
       <c r="AB595" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD595" t="b">
@@ -65463,32 +65463,32 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>129083484</v>
+        <v>129083489</v>
       </c>
       <c r="B596" t="n">
-        <v>88821</v>
+        <v>92810</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E596" t="n">
-        <v>816</v>
+        <v>4362</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>Smultronkantarell</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Aphroditeola olida</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I596" t="inlineStr"/>
@@ -65498,10 +65498,10 @@
         </is>
       </c>
       <c r="Q596" t="n">
-        <v>725274</v>
+        <v>725414</v>
       </c>
       <c r="R596" t="n">
-        <v>7332631</v>
+        <v>7332615</v>
       </c>
       <c r="S596" t="n">
         <v>25</v>
@@ -65533,7 +65533,7 @@
       </c>
       <c r="Z596" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA596" t="inlineStr">
@@ -65543,7 +65543,7 @@
       </c>
       <c r="AB596" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD596" t="b">

--- a/artfynd/A 55345-2020 artfynd.xlsx
+++ b/artfynd/A 55345-2020 artfynd.xlsx
@@ -63736,7 +63736,7 @@
         <v>128759661</v>
       </c>
       <c r="B580" t="n">
-        <v>90149</v>
+        <v>90152</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -63843,7 +63843,7 @@
         <v>128758618</v>
       </c>
       <c r="B581" t="n">
-        <v>90334</v>
+        <v>90337</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -63950,7 +63950,7 @@
         <v>128759259</v>
       </c>
       <c r="B582" t="n">
-        <v>88824</v>
+        <v>88827</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -64057,7 +64057,7 @@
         <v>129083488</v>
       </c>
       <c r="B583" t="n">
-        <v>90555</v>
+        <v>90558</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -64164,7 +64164,7 @@
         <v>129083492</v>
       </c>
       <c r="B584" t="n">
-        <v>91684</v>
+        <v>91687</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -64271,7 +64271,7 @@
         <v>129083476</v>
       </c>
       <c r="B585" t="n">
-        <v>78437</v>
+        <v>78438</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -64378,7 +64378,7 @@
         <v>129083483</v>
       </c>
       <c r="B586" t="n">
-        <v>90555</v>
+        <v>90558</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -64485,7 +64485,7 @@
         <v>129083493</v>
       </c>
       <c r="B587" t="n">
-        <v>90555</v>
+        <v>90558</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -64592,7 +64592,7 @@
         <v>129083482</v>
       </c>
       <c r="B588" t="n">
-        <v>92820</v>
+        <v>92823</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -64699,7 +64699,7 @@
         <v>129083475</v>
       </c>
       <c r="B589" t="n">
-        <v>79624</v>
+        <v>79625</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -64922,7 +64922,7 @@
         <v>129083477</v>
       </c>
       <c r="B591" t="n">
-        <v>90555</v>
+        <v>90558</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -65029,7 +65029,7 @@
         <v>129083485</v>
       </c>
       <c r="B592" t="n">
-        <v>90149</v>
+        <v>90152</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -65133,54 +65133,45 @@
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>129083486</v>
+        <v>129083490</v>
       </c>
       <c r="B593" t="n">
-        <v>57827</v>
+        <v>91687</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E593" t="n">
-        <v>103031</v>
+        <v>1503</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I593" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M593" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr"/>
       <c r="P593" t="inlineStr">
         <is>
           <t>Piellojaure, Lu lm</t>
         </is>
       </c>
       <c r="Q593" t="n">
-        <v>725293</v>
+        <v>725370</v>
       </c>
       <c r="R593" t="n">
-        <v>7332592</v>
+        <v>7332593</v>
       </c>
       <c r="S593" t="n">
         <v>25</v>
@@ -65212,7 +65203,7 @@
       </c>
       <c r="Z593" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA593" t="inlineStr">
@@ -65222,7 +65213,7 @@
       </c>
       <c r="AB593" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD593" t="b">
@@ -65249,45 +65240,54 @@
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>129083490</v>
+        <v>129083486</v>
       </c>
       <c r="B594" t="n">
-        <v>91684</v>
+        <v>57827</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E594" t="n">
-        <v>1503</v>
+        <v>103031</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I594" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P594" t="inlineStr">
         <is>
           <t>Piellojaure, Lu lm</t>
         </is>
       </c>
       <c r="Q594" t="n">
-        <v>725370</v>
+        <v>725293</v>
       </c>
       <c r="R594" t="n">
-        <v>7332593</v>
+        <v>7332592</v>
       </c>
       <c r="S594" t="n">
         <v>25</v>
@@ -65319,7 +65319,7 @@
       </c>
       <c r="Z594" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA594" t="inlineStr">
@@ -65329,7 +65329,7 @@
       </c>
       <c r="AB594" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD594" t="b">
@@ -65359,7 +65359,7 @@
         <v>129083484</v>
       </c>
       <c r="B595" t="n">
-        <v>88824</v>
+        <v>88827</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -65466,7 +65466,7 @@
         <v>129083489</v>
       </c>
       <c r="B596" t="n">
-        <v>92810</v>
+        <v>92813</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>

--- a/artfynd/A 55345-2020 artfynd.xlsx
+++ b/artfynd/A 55345-2020 artfynd.xlsx
@@ -63940,7 +63940,7 @@
       </c>
       <c r="AX581" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY581" t="inlineStr"/>
@@ -65133,45 +65133,54 @@
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>129083490</v>
+        <v>129083486</v>
       </c>
       <c r="B593" t="n">
-        <v>91687</v>
+        <v>57827</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E593" t="n">
-        <v>1503</v>
+        <v>103031</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I593" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M593" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P593" t="inlineStr">
         <is>
           <t>Piellojaure, Lu lm</t>
         </is>
       </c>
       <c r="Q593" t="n">
-        <v>725370</v>
+        <v>725293</v>
       </c>
       <c r="R593" t="n">
-        <v>7332593</v>
+        <v>7332592</v>
       </c>
       <c r="S593" t="n">
         <v>25</v>
@@ -65203,7 +65212,7 @@
       </c>
       <c r="Z593" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA593" t="inlineStr">
@@ -65213,7 +65222,7 @@
       </c>
       <c r="AB593" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD593" t="b">
@@ -65240,54 +65249,45 @@
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>129083486</v>
+        <v>129083490</v>
       </c>
       <c r="B594" t="n">
-        <v>57827</v>
+        <v>91687</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E594" t="n">
-        <v>103031</v>
+        <v>1503</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I594" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M594" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr"/>
       <c r="P594" t="inlineStr">
         <is>
           <t>Piellojaure, Lu lm</t>
         </is>
       </c>
       <c r="Q594" t="n">
-        <v>725293</v>
+        <v>725370</v>
       </c>
       <c r="R594" t="n">
-        <v>7332592</v>
+        <v>7332593</v>
       </c>
       <c r="S594" t="n">
         <v>25</v>
@@ -65319,7 +65319,7 @@
       </c>
       <c r="Z594" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA594" t="inlineStr">
@@ -65329,7 +65329,7 @@
       </c>
       <c r="AB594" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD594" t="b">

--- a/artfynd/A 55345-2020 artfynd.xlsx
+++ b/artfynd/A 55345-2020 artfynd.xlsx
@@ -63940,7 +63940,7 @@
       </c>
       <c r="AX581" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Sara Forsström, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY581" t="inlineStr"/>
@@ -65133,54 +65133,45 @@
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>129083486</v>
+        <v>129083490</v>
       </c>
       <c r="B593" t="n">
-        <v>57827</v>
+        <v>91687</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E593" t="n">
-        <v>103031</v>
+        <v>1503</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I593" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M593" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr"/>
       <c r="P593" t="inlineStr">
         <is>
           <t>Piellojaure, Lu lm</t>
         </is>
       </c>
       <c r="Q593" t="n">
-        <v>725293</v>
+        <v>725370</v>
       </c>
       <c r="R593" t="n">
-        <v>7332592</v>
+        <v>7332593</v>
       </c>
       <c r="S593" t="n">
         <v>25</v>
@@ -65212,7 +65203,7 @@
       </c>
       <c r="Z593" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA593" t="inlineStr">
@@ -65222,7 +65213,7 @@
       </c>
       <c r="AB593" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD593" t="b">
@@ -65249,45 +65240,54 @@
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>129083490</v>
+        <v>129083486</v>
       </c>
       <c r="B594" t="n">
-        <v>91687</v>
+        <v>57827</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E594" t="n">
-        <v>1503</v>
+        <v>103031</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I594" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P594" t="inlineStr">
         <is>
           <t>Piellojaure, Lu lm</t>
         </is>
       </c>
       <c r="Q594" t="n">
-        <v>725370</v>
+        <v>725293</v>
       </c>
       <c r="R594" t="n">
-        <v>7332593</v>
+        <v>7332592</v>
       </c>
       <c r="S594" t="n">
         <v>25</v>
@@ -65319,7 +65319,7 @@
       </c>
       <c r="Z594" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA594" t="inlineStr">
@@ -65329,7 +65329,7 @@
       </c>
       <c r="AB594" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD594" t="b">
@@ -65356,32 +65356,32 @@
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>129083484</v>
+        <v>129083489</v>
       </c>
       <c r="B595" t="n">
-        <v>88827</v>
+        <v>92813</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E595" t="n">
-        <v>816</v>
+        <v>4362</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>Smultronkantarell</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Aphroditeola olida</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I595" t="inlineStr"/>
@@ -65391,10 +65391,10 @@
         </is>
       </c>
       <c r="Q595" t="n">
-        <v>725274</v>
+        <v>725414</v>
       </c>
       <c r="R595" t="n">
-        <v>7332631</v>
+        <v>7332615</v>
       </c>
       <c r="S595" t="n">
         <v>25</v>
@@ -65426,7 +65426,7 @@
       </c>
       <c r="Z595" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA595" t="inlineStr">
@@ -65436,7 +65436,7 @@
       </c>
       <c r="AB595" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD595" t="b">
@@ -65463,32 +65463,32 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>129083489</v>
+        <v>129083484</v>
       </c>
       <c r="B596" t="n">
-        <v>92813</v>
+        <v>88827</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E596" t="n">
-        <v>4362</v>
+        <v>816</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smultronkantarell</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Aphroditeola olida</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
         </is>
       </c>
       <c r="I596" t="inlineStr"/>
@@ -65498,10 +65498,10 @@
         </is>
       </c>
       <c r="Q596" t="n">
-        <v>725414</v>
+        <v>725274</v>
       </c>
       <c r="R596" t="n">
-        <v>7332615</v>
+        <v>7332631</v>
       </c>
       <c r="S596" t="n">
         <v>25</v>
@@ -65533,7 +65533,7 @@
       </c>
       <c r="Z596" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA596" t="inlineStr">
@@ -65543,7 +65543,7 @@
       </c>
       <c r="AB596" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD596" t="b">

--- a/artfynd/A 55345-2020 artfynd.xlsx
+++ b/artfynd/A 55345-2020 artfynd.xlsx
@@ -63736,7 +63736,7 @@
         <v>128759661</v>
       </c>
       <c r="B580" t="n">
-        <v>90152</v>
+        <v>90156</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -63843,7 +63843,7 @@
         <v>128758618</v>
       </c>
       <c r="B581" t="n">
-        <v>90337</v>
+        <v>90341</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -63950,7 +63950,7 @@
         <v>128759259</v>
       </c>
       <c r="B582" t="n">
-        <v>88827</v>
+        <v>88831</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -64057,7 +64057,7 @@
         <v>129083488</v>
       </c>
       <c r="B583" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -64164,7 +64164,7 @@
         <v>129083492</v>
       </c>
       <c r="B584" t="n">
-        <v>91687</v>
+        <v>91694</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -64271,7 +64271,7 @@
         <v>129083476</v>
       </c>
       <c r="B585" t="n">
-        <v>78438</v>
+        <v>78442</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -64378,7 +64378,7 @@
         <v>129083483</v>
       </c>
       <c r="B586" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -64485,7 +64485,7 @@
         <v>129083493</v>
       </c>
       <c r="B587" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -64592,7 +64592,7 @@
         <v>129083482</v>
       </c>
       <c r="B588" t="n">
-        <v>92823</v>
+        <v>92830</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -64699,7 +64699,7 @@
         <v>129083475</v>
       </c>
       <c r="B589" t="n">
-        <v>79625</v>
+        <v>79629</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -64806,7 +64806,7 @@
         <v>129083487</v>
       </c>
       <c r="B590" t="n">
-        <v>57883</v>
+        <v>57885</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -64922,7 +64922,7 @@
         <v>129083477</v>
       </c>
       <c r="B591" t="n">
-        <v>90558</v>
+        <v>90562</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -65029,7 +65029,7 @@
         <v>129083485</v>
       </c>
       <c r="B592" t="n">
-        <v>90152</v>
+        <v>90156</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -65133,45 +65133,54 @@
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>129083490</v>
+        <v>129083486</v>
       </c>
       <c r="B593" t="n">
-        <v>91687</v>
+        <v>57829</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E593" t="n">
-        <v>1503</v>
+        <v>103031</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I593" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M593" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P593" t="inlineStr">
         <is>
           <t>Piellojaure, Lu lm</t>
         </is>
       </c>
       <c r="Q593" t="n">
-        <v>725370</v>
+        <v>725293</v>
       </c>
       <c r="R593" t="n">
-        <v>7332593</v>
+        <v>7332592</v>
       </c>
       <c r="S593" t="n">
         <v>25</v>
@@ -65203,7 +65212,7 @@
       </c>
       <c r="Z593" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA593" t="inlineStr">
@@ -65213,7 +65222,7 @@
       </c>
       <c r="AB593" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD593" t="b">
@@ -65240,54 +65249,45 @@
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>129083486</v>
+        <v>129083490</v>
       </c>
       <c r="B594" t="n">
-        <v>57827</v>
+        <v>91694</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E594" t="n">
-        <v>103031</v>
+        <v>1503</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I594" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M594" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr"/>
       <c r="P594" t="inlineStr">
         <is>
           <t>Piellojaure, Lu lm</t>
         </is>
       </c>
       <c r="Q594" t="n">
-        <v>725293</v>
+        <v>725370</v>
       </c>
       <c r="R594" t="n">
-        <v>7332592</v>
+        <v>7332593</v>
       </c>
       <c r="S594" t="n">
         <v>25</v>
@@ -65319,7 +65319,7 @@
       </c>
       <c r="Z594" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA594" t="inlineStr">
@@ -65329,7 +65329,7 @@
       </c>
       <c r="AB594" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD594" t="b">
@@ -65359,7 +65359,7 @@
         <v>129083489</v>
       </c>
       <c r="B595" t="n">
-        <v>92813</v>
+        <v>92820</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -65466,7 +65466,7 @@
         <v>129083484</v>
       </c>
       <c r="B596" t="n">
-        <v>88827</v>
+        <v>88831</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>

--- a/artfynd/A 55345-2020 artfynd.xlsx
+++ b/artfynd/A 55345-2020 artfynd.xlsx
@@ -65356,32 +65356,32 @@
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>129083489</v>
+        <v>129083484</v>
       </c>
       <c r="B595" t="n">
-        <v>92820</v>
+        <v>88831</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E595" t="n">
-        <v>4362</v>
+        <v>816</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smultronkantarell</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Aphroditeola olida</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
         </is>
       </c>
       <c r="I595" t="inlineStr"/>
@@ -65391,10 +65391,10 @@
         </is>
       </c>
       <c r="Q595" t="n">
-        <v>725414</v>
+        <v>725274</v>
       </c>
       <c r="R595" t="n">
-        <v>7332615</v>
+        <v>7332631</v>
       </c>
       <c r="S595" t="n">
         <v>25</v>
@@ -65426,7 +65426,7 @@
       </c>
       <c r="Z595" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA595" t="inlineStr">
@@ -65436,7 +65436,7 @@
       </c>
       <c r="AB595" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD595" t="b">
@@ -65463,32 +65463,32 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>129083484</v>
+        <v>129083489</v>
       </c>
       <c r="B596" t="n">
-        <v>88831</v>
+        <v>92820</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E596" t="n">
-        <v>816</v>
+        <v>4362</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>Smultronkantarell</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Aphroditeola olida</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I596" t="inlineStr"/>
@@ -65498,10 +65498,10 @@
         </is>
       </c>
       <c r="Q596" t="n">
-        <v>725274</v>
+        <v>725414</v>
       </c>
       <c r="R596" t="n">
-        <v>7332631</v>
+        <v>7332615</v>
       </c>
       <c r="S596" t="n">
         <v>25</v>
@@ -65533,7 +65533,7 @@
       </c>
       <c r="Z596" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA596" t="inlineStr">
@@ -65543,7 +65543,7 @@
       </c>
       <c r="AB596" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD596" t="b">

--- a/artfynd/A 55345-2020 artfynd.xlsx
+++ b/artfynd/A 55345-2020 artfynd.xlsx
@@ -63736,7 +63736,7 @@
         <v>128759661</v>
       </c>
       <c r="B580" t="n">
-        <v>90156</v>
+        <v>90163</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -63833,7 +63833,7 @@
       </c>
       <c r="AX580" t="inlineStr">
         <is>
-          <t>Sara Forsström, Isak Vahlström</t>
+          <t>Isak Vahlström, Sara Forsström</t>
         </is>
       </c>
       <c r="AY580" t="inlineStr"/>
@@ -63843,7 +63843,7 @@
         <v>128758618</v>
       </c>
       <c r="B581" t="n">
-        <v>90341</v>
+        <v>90348</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -63950,7 +63950,7 @@
         <v>128759259</v>
       </c>
       <c r="B582" t="n">
-        <v>88831</v>
+        <v>88838</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -64057,7 +64057,7 @@
         <v>129083488</v>
       </c>
       <c r="B583" t="n">
-        <v>90562</v>
+        <v>90569</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -64164,7 +64164,7 @@
         <v>129083492</v>
       </c>
       <c r="B584" t="n">
-        <v>91694</v>
+        <v>91701</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -64378,7 +64378,7 @@
         <v>129083483</v>
       </c>
       <c r="B586" t="n">
-        <v>90562</v>
+        <v>90569</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -64485,7 +64485,7 @@
         <v>129083493</v>
       </c>
       <c r="B587" t="n">
-        <v>90562</v>
+        <v>90569</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -64592,7 +64592,7 @@
         <v>129083482</v>
       </c>
       <c r="B588" t="n">
-        <v>92830</v>
+        <v>92837</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -64922,7 +64922,7 @@
         <v>129083477</v>
       </c>
       <c r="B591" t="n">
-        <v>90562</v>
+        <v>90569</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -65029,7 +65029,7 @@
         <v>129083485</v>
       </c>
       <c r="B592" t="n">
-        <v>90156</v>
+        <v>90163</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -65133,54 +65133,45 @@
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>129083486</v>
+        <v>129083490</v>
       </c>
       <c r="B593" t="n">
-        <v>57829</v>
+        <v>91701</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E593" t="n">
-        <v>103031</v>
+        <v>1503</v>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>Lavskrika</t>
+          <t>Gräddporing</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>Perisoreus infaustus</t>
+          <t>Sidera lenis</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I593" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M593" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Miettinen</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr"/>
       <c r="P593" t="inlineStr">
         <is>
           <t>Piellojaure, Lu lm</t>
         </is>
       </c>
       <c r="Q593" t="n">
-        <v>725293</v>
+        <v>725370</v>
       </c>
       <c r="R593" t="n">
-        <v>7332592</v>
+        <v>7332593</v>
       </c>
       <c r="S593" t="n">
         <v>25</v>
@@ -65212,7 +65203,7 @@
       </c>
       <c r="Z593" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA593" t="inlineStr">
@@ -65222,7 +65213,7 @@
       </c>
       <c r="AB593" t="inlineStr">
         <is>
-          <t>15:26</t>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AD593" t="b">
@@ -65249,45 +65240,54 @@
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>129083490</v>
+        <v>129083486</v>
       </c>
       <c r="B594" t="n">
-        <v>91694</v>
+        <v>57829</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E594" t="n">
-        <v>1503</v>
+        <v>103031</v>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>Gräddporing</t>
+          <t>Lavskrika</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>Sidera lenis</t>
+          <t>Perisoreus infaustus</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>(P.Karst.) Miettinen</t>
-        </is>
-      </c>
-      <c r="I594" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M594" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P594" t="inlineStr">
         <is>
           <t>Piellojaure, Lu lm</t>
         </is>
       </c>
       <c r="Q594" t="n">
-        <v>725370</v>
+        <v>725293</v>
       </c>
       <c r="R594" t="n">
-        <v>7332593</v>
+        <v>7332592</v>
       </c>
       <c r="S594" t="n">
         <v>25</v>
@@ -65319,7 +65319,7 @@
       </c>
       <c r="Z594" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AA594" t="inlineStr">
@@ -65329,7 +65329,7 @@
       </c>
       <c r="AB594" t="inlineStr">
         <is>
-          <t>15:09</t>
+          <t>15:26</t>
         </is>
       </c>
       <c r="AD594" t="b">
@@ -65359,7 +65359,7 @@
         <v>129083484</v>
       </c>
       <c r="B595" t="n">
-        <v>88831</v>
+        <v>88838</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -65466,7 +65466,7 @@
         <v>129083489</v>
       </c>
       <c r="B596" t="n">
-        <v>92820</v>
+        <v>92827</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>

--- a/artfynd/A 55345-2020 artfynd.xlsx
+++ b/artfynd/A 55345-2020 artfynd.xlsx
@@ -63736,7 +63736,7 @@
         <v>128759661</v>
       </c>
       <c r="B580" t="n">
-        <v>90163</v>
+        <v>90165</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -63833,7 +63833,7 @@
       </c>
       <c r="AX580" t="inlineStr">
         <is>
-          <t>Isak Vahlström, Sara Forsström</t>
+          <t>Sara Forsström, Isak Vahlström</t>
         </is>
       </c>
       <c r="AY580" t="inlineStr"/>
@@ -63843,7 +63843,7 @@
         <v>128758618</v>
       </c>
       <c r="B581" t="n">
-        <v>90348</v>
+        <v>90350</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -63950,7 +63950,7 @@
         <v>128759259</v>
       </c>
       <c r="B582" t="n">
-        <v>88838</v>
+        <v>88840</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -64057,7 +64057,7 @@
         <v>129083488</v>
       </c>
       <c r="B583" t="n">
-        <v>90569</v>
+        <v>90571</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -64164,7 +64164,7 @@
         <v>129083492</v>
       </c>
       <c r="B584" t="n">
-        <v>91701</v>
+        <v>91703</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -64271,7 +64271,7 @@
         <v>129083476</v>
       </c>
       <c r="B585" t="n">
-        <v>78442</v>
+        <v>78444</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -64378,7 +64378,7 @@
         <v>129083483</v>
       </c>
       <c r="B586" t="n">
-        <v>90569</v>
+        <v>90571</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -64485,7 +64485,7 @@
         <v>129083493</v>
       </c>
       <c r="B587" t="n">
-        <v>90569</v>
+        <v>90571</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -64592,7 +64592,7 @@
         <v>129083482</v>
       </c>
       <c r="B588" t="n">
-        <v>92837</v>
+        <v>92839</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -64699,7 +64699,7 @@
         <v>129083475</v>
       </c>
       <c r="B589" t="n">
-        <v>79629</v>
+        <v>79631</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -64806,7 +64806,7 @@
         <v>129083487</v>
       </c>
       <c r="B590" t="n">
-        <v>57885</v>
+        <v>57887</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -64922,7 +64922,7 @@
         <v>129083477</v>
       </c>
       <c r="B591" t="n">
-        <v>90569</v>
+        <v>90571</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -65029,7 +65029,7 @@
         <v>129083485</v>
       </c>
       <c r="B592" t="n">
-        <v>90163</v>
+        <v>90165</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -65136,7 +65136,7 @@
         <v>129083490</v>
       </c>
       <c r="B593" t="n">
-        <v>91701</v>
+        <v>91703</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -65243,7 +65243,7 @@
         <v>129083486</v>
       </c>
       <c r="B594" t="n">
-        <v>57829</v>
+        <v>57831</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -65359,7 +65359,7 @@
         <v>129083484</v>
       </c>
       <c r="B595" t="n">
-        <v>88838</v>
+        <v>88840</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -65466,7 +65466,7 @@
         <v>129083489</v>
       </c>
       <c r="B596" t="n">
-        <v>92827</v>
+        <v>92829</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>

--- a/artfynd/A 55345-2020 artfynd.xlsx
+++ b/artfynd/A 55345-2020 artfynd.xlsx
@@ -65356,32 +65356,32 @@
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>129083484</v>
+        <v>129083489</v>
       </c>
       <c r="B595" t="n">
-        <v>88840</v>
+        <v>92829</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E595" t="n">
-        <v>816</v>
+        <v>4362</v>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>Smultronkantarell</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>Aphroditeola olida</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
         <is>
-          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I595" t="inlineStr"/>
@@ -65391,10 +65391,10 @@
         </is>
       </c>
       <c r="Q595" t="n">
-        <v>725274</v>
+        <v>725414</v>
       </c>
       <c r="R595" t="n">
-        <v>7332631</v>
+        <v>7332615</v>
       </c>
       <c r="S595" t="n">
         <v>25</v>
@@ -65426,7 +65426,7 @@
       </c>
       <c r="Z595" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA595" t="inlineStr">
@@ -65436,7 +65436,7 @@
       </c>
       <c r="AB595" t="inlineStr">
         <is>
-          <t>15:40</t>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AD595" t="b">
@@ -65463,32 +65463,32 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>129083489</v>
+        <v>129083484</v>
       </c>
       <c r="B596" t="n">
-        <v>92829</v>
+        <v>88840</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E596" t="n">
-        <v>4362</v>
+        <v>816</v>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Smultronkantarell</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Aphroditeola olida</t>
         </is>
       </c>
       <c r="H596" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Quél.) Redhead &amp; Manfr.Binder</t>
         </is>
       </c>
       <c r="I596" t="inlineStr"/>
@@ -65498,10 +65498,10 @@
         </is>
       </c>
       <c r="Q596" t="n">
-        <v>725414</v>
+        <v>725274</v>
       </c>
       <c r="R596" t="n">
-        <v>7332615</v>
+        <v>7332631</v>
       </c>
       <c r="S596" t="n">
         <v>25</v>
@@ -65533,7 +65533,7 @@
       </c>
       <c r="Z596" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AA596" t="inlineStr">
@@ -65543,7 +65543,7 @@
       </c>
       <c r="AB596" t="inlineStr">
         <is>
-          <t>15:12</t>
+          <t>15:40</t>
         </is>
       </c>
       <c r="AD596" t="b">
